--- a/機械惑星マップ構造.xlsx
+++ b/機械惑星マップ構造.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\新しいフォルダー\就職作品　制作\企画書・仕様書\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\就職作品\マップ\Unity_Zishu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{87E6B8A2-E2FE-48EF-BAE5-2A0524D5538F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D18B644-35EF-4697-BB74-5EBFB6219F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="765" yWindow="-12495" windowWidth="19980" windowHeight="12510" xr2:uid="{17295954-BBC4-4D7A-9D84-75ABB5B6BC55}"/>
+    <workbookView xWindow="6450" yWindow="3585" windowWidth="16710" windowHeight="11295" xr2:uid="{17295954-BBC4-4D7A-9D84-75ABB5B6BC55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -133,56 +133,7 @@
   <cellStyles count="1">
     <cellStyle name="標準" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF002060"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="4"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="7"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="9" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFFF00"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="8">
     <dxf>
       <fill>
         <patternFill>
@@ -3794,28 +3745,28 @@
   </sheetData>
   <phoneticPr fontId="1"/>
   <conditionalFormatting sqref="A1:XFD1048576">
-    <cfRule type="containsText" dxfId="0" priority="8" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="7" priority="8" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="1" priority="7" operator="containsText" text="1">
+    <cfRule type="containsText" dxfId="6" priority="7" operator="containsText" text="1">
       <formula>NOT(ISERROR(SEARCH("1",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="2" priority="6" operator="containsText" text="2">
+    <cfRule type="containsText" dxfId="5" priority="6" operator="containsText" text="2">
       <formula>NOT(ISERROR(SEARCH("2",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="3" priority="5" operator="containsText" text="01">
+    <cfRule type="containsText" dxfId="4" priority="5" operator="containsText" text="01">
       <formula>NOT(ISERROR(SEARCH("01",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="4" priority="4" operator="containsText" text="3">
+    <cfRule type="containsText" dxfId="3" priority="4" operator="containsText" text="3">
       <formula>NOT(ISERROR(SEARCH("3",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="4">
+    <cfRule type="containsText" dxfId="2" priority="3" operator="containsText" text="4">
       <formula>NOT(ISERROR(SEARCH("4",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="6" priority="2" operator="containsText" text="5">
+    <cfRule type="containsText" dxfId="1" priority="2" operator="containsText" text="5">
       <formula>NOT(ISERROR(SEARCH("5",A1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="7" priority="1" operator="containsText" text="6">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="6">
       <formula>NOT(ISERROR(SEARCH("6",A1)))</formula>
     </cfRule>
   </conditionalFormatting>

--- a/機械惑星マップ構造.xlsx
+++ b/機械惑星マップ構造.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Akiyoshi\就職作品\マップ\Unity_Zishu\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1D18B644-35EF-4697-BB74-5EBFB6219F6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7FBBCD-8722-4479-9AB9-D7C3DC5A65C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6450" yWindow="3585" windowWidth="16710" windowHeight="11295" xr2:uid="{17295954-BBC4-4D7A-9D84-75ABB5B6BC55}"/>
+    <workbookView xWindow="960" yWindow="-10140" windowWidth="16710" windowHeight="11295" xr2:uid="{17295954-BBC4-4D7A-9D84-75ABB5B6BC55}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
